--- a/output/pdf_financials_xlsx/ECM.H.xlsx
+++ b/output/pdf_financials_xlsx/ECM.H.xlsx
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.438181</v>
+        <v>1.891486</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.610203</v>
+        <v>7.3431</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.70612</v>
+        <v>2.053694</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.135357</v>
+        <v>1.419118</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -1931,10 +1931,10 @@
         <v>1.908187</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.3078</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.331573</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.404963</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.105268</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.088272</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.119331</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.010196</v>
       </c>
     </row>
     <row r="35">
@@ -2019,10 +2019,10 @@
         <v>1.908187</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.3078</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.331573</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -2030,19 +2030,19 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>4.404963</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.105268</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.088272</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.119331</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.010196</v>
       </c>
     </row>
     <row r="37">
@@ -2547,10 +2547,10 @@
         <v>2.325516</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.8749169999999999</v>
+        <v>0.567117</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.504485</v>
+        <v>0.172912</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -2558,19 +2558,19 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.055427</v>
+        <v>0.650464</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.384579</v>
+        <v>0.279311</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.823565</v>
+        <v>0.704234</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1966</v>
+        <v>0.186404</v>
       </c>
     </row>
     <row r="49">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">

--- a/output/pdf_financials_xlsx/ECM.H.xlsx
+++ b/output/pdf_financials_xlsx/ECM.H.xlsx
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.129039</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.719967</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>1.02033</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.022129</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -1735,16 +1735,16 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.825585</v>
+        <v>-0.696546</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.129748</v>
+        <v>-0.409781</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.924928</v>
+        <v>-3.904598</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.006353</v>
+        <v>-3.984224</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-3.314362</v>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-2503.43267573846</v>
+        <v>-1984.779923447214</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-654.3292001750822</v>
+        <v>-650.7150276668997</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>-255.0639360208831</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.280753</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.280753</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.280753</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.070184</v>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
@@ -4829,16 +4829,16 @@
         </is>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.129039</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.719967</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.02033</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.022129</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -16975,7 +16975,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -18040,7 +18044,11 @@
           <t>Depreciation of property, plant and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -18316,7 +18324,11 @@
           <t>Depreciation of right of use assets (Note 7)</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -20008,7 +20020,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -20077,7 +20093,11 @@
           <t>Depreciation of right of use assets</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -21351,7 +21371,11 @@
           <t>Depreciation of right of use assets</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -22562,7 +22586,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -23976,7 +24000,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -24905,7 +24929,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">

--- a/output/pdf_financials_xlsx/ECM.H.xlsx
+++ b/output/pdf_financials_xlsx/ECM.H.xlsx
@@ -2215,10 +2215,10 @@
         <v>0.311407</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.000529</v>
       </c>
     </row>
     <row r="41">
@@ -2259,10 +2259,10 @@
         <v>0.622814</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.318071</v>
+        <v>0.319271</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.262721</v>
+        <v>0.26325</v>
       </c>
     </row>
     <row r="42">
@@ -2567,10 +2567,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.704234</v>
+        <v>0.703034</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.186404</v>
+        <v>0.185875</v>
       </c>
     </row>
     <row r="49">
@@ -19103,7 +19103,11 @@
           <t>Private placement (Note 14)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
